--- a/staff_forms/020_employee_reference_check_form--staff_forms.xlsx
+++ b/staff_forms/020_employee_reference_check_form--staff_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Job Title</t>
+          <t>Job Title2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -851,7 +851,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Years Worked</t>
+          <t>Years Worked2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -947,7 +947,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Last Evaluation</t>
+          <t>Last Evaluation2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -970,7 +970,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Job Title</t>
+          <t>Job Title3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -993,7 +993,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Date of Birth</t>
+          <t>Date Of Birth2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Years Worked</t>
+          <t>Years Worked3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Last Salary</t>
+          <t>Last Salary2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Employee Notes</t>
+          <t>Employee Notes2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
